--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-4634fc2c</v>
+        <v>QT-OPP-8f010ca6</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-8f010ca6</v>
+        <v>QT-OPP-1c22aa91</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-1c22aa91</v>
+        <v>QT-OPP-f9964e9b</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-f9964e9b</v>
+        <v>QT-OPP-e8481f24</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-e8481f24</v>
+        <v>QT-OPP-99479abb</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-99479abb</v>
+        <v>QT-OPP-52bdd934</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-52bdd934</v>
+        <v>QT-OPP-09463e7d</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-09463e7d</v>
+        <v>QT-OPP-dc7f5f07</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-dc7f5f07</v>
+        <v>QT-OPP-74285fd3</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-74285fd3</v>
+        <v>QT-OPP-54f7043a</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-54f7043a</v>
+        <v>QT-OPP-454316d2</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-454316d2</v>
+        <v>QT-OPP-ee14c90b</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-ee14c90b</v>
+        <v>QT-OPP-6c0f243a</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-6c0f243a</v>
+        <v>QT-OPP-ef89d983</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-internal-pricing-proof.xlsx
@@ -428,7 +428,7 @@
         <v>Quotation</v>
       </c>
       <c r="B3" t="str">
-        <v>QT-OPP-ef89d983</v>
+        <v>QT-OPP-3e942e90</v>
       </c>
     </row>
     <row r="4">
